--- a/Desktop Files - Mix/02. Data - EclipseApps/01. Live Project/10. CSR_HEAD.xlsx
+++ b/Desktop Files - Mix/02. Data - EclipseApps/01. Live Project/10. CSR_HEAD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Visteon\00. Visteon Copy\ZPLM\GAP 33\06. CS Request\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05. Daily (21-Mar-26) - 6GB\VSCode\Desktop Files - Mix\02. Data - EclipseApps\01. Live Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498B365A-B20F-4173-825A-63AD2A92149E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD6A73D-8C96-4A58-82B5-1B558DAC8091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -622,17 +622,8 @@
       <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="L2">
-        <v>20250427153858.102</v>
-      </c>
       <c r="M2" t="s">
         <v>21</v>
-      </c>
-      <c r="N2">
-        <v>20250427154425.699</v>
-      </c>
-      <c r="O2">
-        <v>20250427154425.699</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -660,17 +651,8 @@
       <c r="K3" t="s">
         <v>21</v>
       </c>
-      <c r="L3">
-        <v>20250427164016.301</v>
-      </c>
       <c r="M3" t="s">
         <v>21</v>
-      </c>
-      <c r="N3">
-        <v>20250427164016.301</v>
-      </c>
-      <c r="O3">
-        <v>20250427164016.301</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -698,18 +680,9 @@
       <c r="K4" t="s">
         <v>27</v>
       </c>
-      <c r="L4">
-        <v>20250502184251.898</v>
-      </c>
       <c r="M4" t="s">
         <v>27</v>
       </c>
-      <c r="N4">
-        <v>20250502184251.898</v>
-      </c>
-      <c r="O4">
-        <v>20250502184251.898</v>
-      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -736,18 +709,9 @@
       <c r="K5" t="s">
         <v>27</v>
       </c>
-      <c r="L5">
-        <v>20250502184216.699</v>
-      </c>
       <c r="M5" t="s">
         <v>27</v>
       </c>
-      <c r="N5">
-        <v>20250502185937.5</v>
-      </c>
-      <c r="O5">
-        <v>20250502185937.5</v>
-      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -774,17 +738,8 @@
       <c r="K6" t="s">
         <v>21</v>
       </c>
-      <c r="L6">
-        <v>20250504015846.699</v>
-      </c>
       <c r="M6" t="s">
         <v>21</v>
-      </c>
-      <c r="N6">
-        <v>20250504015846.699</v>
-      </c>
-      <c r="O6">
-        <v>20250504015846.699</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -812,17 +767,8 @@
       <c r="K7" t="s">
         <v>21</v>
       </c>
-      <c r="L7">
-        <v>20250504015846.699</v>
-      </c>
       <c r="M7" t="s">
         <v>21</v>
-      </c>
-      <c r="N7">
-        <v>20250504022453.699</v>
-      </c>
-      <c r="O7">
-        <v>20250504022453.699</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -850,17 +796,8 @@
       <c r="K8" t="s">
         <v>21</v>
       </c>
-      <c r="L8">
-        <v>20250504024600.801</v>
-      </c>
       <c r="M8" t="s">
         <v>21</v>
-      </c>
-      <c r="N8">
-        <v>20250504024735.199</v>
-      </c>
-      <c r="O8">
-        <v>20250504024735.199</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -888,17 +825,8 @@
       <c r="K9" t="s">
         <v>21</v>
       </c>
-      <c r="L9">
-        <v>20250504030326.898</v>
-      </c>
       <c r="M9" t="s">
         <v>21</v>
-      </c>
-      <c r="N9">
-        <v>20250504030342</v>
-      </c>
-      <c r="O9">
-        <v>20250504030342</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -926,17 +854,8 @@
       <c r="K10" t="s">
         <v>21</v>
       </c>
-      <c r="L10">
-        <v>20250504040251.398</v>
-      </c>
       <c r="M10" t="s">
         <v>21</v>
-      </c>
-      <c r="N10">
-        <v>20250504040827.699</v>
-      </c>
-      <c r="O10">
-        <v>20250504040827.699</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -964,17 +883,8 @@
       <c r="K11" t="s">
         <v>21</v>
       </c>
-      <c r="L11">
-        <v>20250504035904.602</v>
-      </c>
       <c r="M11" t="s">
         <v>21</v>
-      </c>
-      <c r="N11">
-        <v>20250504040836.898</v>
-      </c>
-      <c r="O11">
-        <v>20250504040836.898</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -1002,17 +912,8 @@
       <c r="K12" t="s">
         <v>21</v>
       </c>
-      <c r="L12">
-        <v>20250504033634.898</v>
-      </c>
       <c r="M12" t="s">
         <v>21</v>
-      </c>
-      <c r="N12">
-        <v>20250504040845.5</v>
-      </c>
-      <c r="O12">
-        <v>20250504040845.5</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -1040,17 +941,8 @@
       <c r="K13" t="s">
         <v>21</v>
       </c>
-      <c r="L13">
-        <v>20250504033635</v>
-      </c>
       <c r="M13" t="s">
         <v>21</v>
-      </c>
-      <c r="N13">
-        <v>20250504040851.699</v>
-      </c>
-      <c r="O13">
-        <v>20250504040851.699</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -1078,17 +970,8 @@
       <c r="K14" t="s">
         <v>21</v>
       </c>
-      <c r="L14">
-        <v>20250504015846.699</v>
-      </c>
       <c r="M14" t="s">
         <v>21</v>
-      </c>
-      <c r="N14">
-        <v>20250504040859.5</v>
-      </c>
-      <c r="O14">
-        <v>20250504040859.5</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -1116,17 +999,8 @@
       <c r="K15" t="s">
         <v>21</v>
       </c>
-      <c r="L15">
-        <v>20250504040251.398</v>
-      </c>
       <c r="M15" t="s">
         <v>21</v>
-      </c>
-      <c r="N15">
-        <v>20250504040939.102</v>
-      </c>
-      <c r="O15">
-        <v>20250504040939.102</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -1154,20 +1028,11 @@
       <c r="K16" t="s">
         <v>21</v>
       </c>
-      <c r="L16">
-        <v>20250504041534.699</v>
-      </c>
       <c r="M16" t="s">
         <v>21</v>
       </c>
-      <c r="N16">
-        <v>20250504041548</v>
-      </c>
-      <c r="O16">
-        <v>20250504041548</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>66</v>
       </c>
@@ -1192,20 +1057,11 @@
       <c r="K17" t="s">
         <v>21</v>
       </c>
-      <c r="L17">
-        <v>20250504041715.898</v>
-      </c>
       <c r="M17" t="s">
         <v>21</v>
       </c>
-      <c r="N17">
-        <v>20250504041726.301</v>
-      </c>
-      <c r="O17">
-        <v>20250504041726.301</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>66</v>
       </c>
@@ -1230,20 +1086,11 @@
       <c r="K18" t="s">
         <v>21</v>
       </c>
-      <c r="L18">
-        <v>20250504041802.301</v>
-      </c>
       <c r="M18" t="s">
         <v>21</v>
       </c>
-      <c r="N18">
-        <v>20250504041913.801</v>
-      </c>
-      <c r="O18">
-        <v>20250504041913.801</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>66</v>
       </c>
@@ -1268,20 +1115,11 @@
       <c r="K19" t="s">
         <v>21</v>
       </c>
-      <c r="L19">
-        <v>20250504041949.5</v>
-      </c>
       <c r="M19" t="s">
         <v>21</v>
       </c>
-      <c r="N19">
-        <v>20250504042430.398</v>
-      </c>
-      <c r="O19">
-        <v>20250504042430.398</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>66</v>
       </c>
@@ -1306,20 +1144,11 @@
       <c r="K20" t="s">
         <v>21</v>
       </c>
-      <c r="L20">
-        <v>20250504043538.301</v>
-      </c>
       <c r="M20" t="s">
         <v>21</v>
       </c>
-      <c r="N20">
-        <v>20250504043550.301</v>
-      </c>
-      <c r="O20">
-        <v>20250504043550.301</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>66</v>
       </c>
@@ -1344,20 +1173,11 @@
       <c r="K21" t="s">
         <v>21</v>
       </c>
-      <c r="L21">
-        <v>20250504044607.699</v>
-      </c>
       <c r="M21" t="s">
         <v>21</v>
       </c>
-      <c r="N21">
-        <v>20250504045031.301</v>
-      </c>
-      <c r="O21">
-        <v>20250504045031.301</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>66</v>
       </c>
@@ -1382,20 +1202,11 @@
       <c r="K22" t="s">
         <v>21</v>
       </c>
-      <c r="L22">
-        <v>20250504045115.5</v>
-      </c>
       <c r="M22" t="s">
         <v>21</v>
       </c>
-      <c r="N22">
-        <v>20250504050003.602</v>
-      </c>
-      <c r="O22">
-        <v>20250504050003.602</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>66</v>
       </c>
@@ -1420,20 +1231,11 @@
       <c r="K23" t="s">
         <v>21</v>
       </c>
-      <c r="L23">
-        <v>20250504050440.699</v>
-      </c>
       <c r="M23" t="s">
         <v>21</v>
       </c>
-      <c r="N23">
-        <v>20250504050457.5</v>
-      </c>
-      <c r="O23">
-        <v>20250504050457.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>66</v>
       </c>
@@ -1458,20 +1260,11 @@
       <c r="K24" t="s">
         <v>21</v>
       </c>
-      <c r="L24">
-        <v>20250504050406.301</v>
-      </c>
       <c r="M24" t="s">
         <v>21</v>
       </c>
-      <c r="N24">
-        <v>20250504050709.898</v>
-      </c>
-      <c r="O24">
-        <v>20250504050709.898</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -1496,20 +1289,11 @@
       <c r="K25" t="s">
         <v>21</v>
       </c>
-      <c r="L25">
-        <v>20250504052955.398</v>
-      </c>
       <c r="M25" t="s">
         <v>21</v>
       </c>
-      <c r="N25">
-        <v>20250504053006.801</v>
-      </c>
-      <c r="O25">
-        <v>20250504053006.801</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>66</v>
       </c>
@@ -1534,20 +1318,11 @@
       <c r="K26" t="s">
         <v>21</v>
       </c>
-      <c r="L26">
-        <v>20250504053634.301</v>
-      </c>
       <c r="M26" t="s">
         <v>21</v>
       </c>
-      <c r="N26">
-        <v>20250504053643.602</v>
-      </c>
-      <c r="O26">
-        <v>20250504053643.602</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>66</v>
       </c>
@@ -1572,20 +1347,11 @@
       <c r="K27" t="s">
         <v>21</v>
       </c>
-      <c r="L27">
-        <v>20250504054321.602</v>
-      </c>
       <c r="M27" t="s">
         <v>21</v>
       </c>
-      <c r="N27">
-        <v>20250504054559.199</v>
-      </c>
-      <c r="O27">
-        <v>20250504054559.199</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>66</v>
       </c>
@@ -1610,20 +1376,11 @@
       <c r="K28" t="s">
         <v>21</v>
       </c>
-      <c r="L28">
-        <v>20250504054732.898</v>
-      </c>
       <c r="M28" t="s">
         <v>21</v>
       </c>
-      <c r="N28">
-        <v>20250504054738.699</v>
-      </c>
-      <c r="O28">
-        <v>20250504054738.699</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>66</v>
       </c>
@@ -1651,20 +1408,11 @@
       <c r="K29" t="s">
         <v>21</v>
       </c>
-      <c r="L29">
-        <v>20250504150803.301</v>
-      </c>
       <c r="M29" t="s">
         <v>21</v>
       </c>
-      <c r="N29">
-        <v>20250504211930</v>
-      </c>
-      <c r="O29">
-        <v>20250504211930</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>66</v>
       </c>
@@ -1689,20 +1437,11 @@
       <c r="K30" t="s">
         <v>21</v>
       </c>
-      <c r="L30">
-        <v>20250504055303.301</v>
-      </c>
       <c r="M30" t="s">
         <v>21</v>
       </c>
-      <c r="N30">
-        <v>20250504212302.5</v>
-      </c>
-      <c r="O30">
-        <v>20250504212302.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>66</v>
       </c>
@@ -1727,20 +1466,11 @@
       <c r="K31" t="s">
         <v>21</v>
       </c>
-      <c r="L31">
-        <v>20250504054929.301</v>
-      </c>
       <c r="M31" t="s">
         <v>21</v>
       </c>
-      <c r="N31">
-        <v>20250504212826.301</v>
-      </c>
-      <c r="O31">
-        <v>20250504212826.301</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>66</v>
       </c>
@@ -1765,20 +1495,11 @@
       <c r="K32" t="s">
         <v>21</v>
       </c>
-      <c r="L32">
-        <v>20250506022053.699</v>
-      </c>
       <c r="M32" t="s">
         <v>21</v>
       </c>
-      <c r="N32">
-        <v>20250506022053.699</v>
-      </c>
-      <c r="O32">
-        <v>20250506022053.699</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>66</v>
       </c>
@@ -1803,20 +1524,11 @@
       <c r="K33" t="s">
         <v>21</v>
       </c>
-      <c r="L33">
-        <v>20250506221433.898</v>
-      </c>
       <c r="M33" t="s">
         <v>21</v>
       </c>
-      <c r="N33">
-        <v>20250506221541.199</v>
-      </c>
-      <c r="O33">
-        <v>20250506221541.199</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
@@ -1841,20 +1553,11 @@
       <c r="K34" t="s">
         <v>21</v>
       </c>
-      <c r="L34">
-        <v>20250506235342.5</v>
-      </c>
       <c r="M34" t="s">
         <v>21</v>
       </c>
-      <c r="N34">
-        <v>20250506235403.5</v>
-      </c>
-      <c r="O34">
-        <v>20250506235403.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>66</v>
       </c>
@@ -1879,20 +1582,11 @@
       <c r="K35" t="s">
         <v>21</v>
       </c>
-      <c r="L35">
-        <v>20250506235435.699</v>
-      </c>
       <c r="M35" t="s">
         <v>21</v>
       </c>
-      <c r="N35">
-        <v>20250509022613.5</v>
-      </c>
-      <c r="O35">
-        <v>20250509022613.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>66</v>
       </c>
@@ -1920,20 +1614,11 @@
       <c r="K36" t="s">
         <v>21</v>
       </c>
-      <c r="L36">
-        <v>20250428111148.5</v>
-      </c>
       <c r="M36" t="s">
         <v>21</v>
       </c>
-      <c r="N36">
-        <v>20250509023203.801</v>
-      </c>
-      <c r="O36">
-        <v>20250509023203.801</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>66</v>
       </c>
@@ -1961,20 +1646,11 @@
       <c r="K37" t="s">
         <v>21</v>
       </c>
-      <c r="L37">
-        <v>20250427153439.102</v>
-      </c>
       <c r="M37" t="s">
         <v>21</v>
       </c>
-      <c r="N37">
-        <v>20250428111017.699</v>
-      </c>
-      <c r="O37">
-        <v>20250428111017.699</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>66</v>
       </c>
@@ -1999,17 +1675,8 @@
       <c r="K38" t="s">
         <v>21</v>
       </c>
-      <c r="L38">
-        <v>20250427164016.301</v>
-      </c>
       <c r="M38" t="s">
         <v>21</v>
-      </c>
-      <c r="N38">
-        <v>20250427165101.602</v>
-      </c>
-      <c r="O38">
-        <v>20250427165101.602</v>
       </c>
     </row>
   </sheetData>
